--- a/incoming-freightiq/CE & SF Combined_Transaction Report (8).xlsx
+++ b/incoming-freightiq/CE & SF Combined_Transaction Report (8).xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="389">
   <si>
     <t>CE &amp; SF Combined</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Transaction Report</t>
   </si>
   <si>
-    <t>January 1-May 25, 2026</t>
+    <t>January 1-May 30, 2026</t>
   </si>
   <si>
     <t>Truck/Trailer</t>
@@ -363,6 +363,18 @@
     <t>ORIG CO NAME:WEX INC ORIG ID:XXXXXX8050 DESC DATE:SD0934 CO ENTRY DESCR:EFSLLC SEC:CCD TRACE#:XXXXXXXX5933443 EED:260522 IND ID:XXXXXXXX00387 IND NAME:SHOW FREI GHT INC . TRN: XXXXXX3443 TC</t>
   </si>
   <si>
+    <t>05/26/2026</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:WEX INC ORIG ID:XXXXXX8050 DESC DATE:SD0926 CO ENTRY DESCR:EFSLLC SEC:CCD TRACE#:XXXXXXXX2414899 EED:260526 IND ID:XXXXXXXX00387 IND NAME:SHOW FREI GHT INC . TRN: XXXXXX4899 TC</t>
+  </si>
+  <si>
+    <t>05/29/2026</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:WEX INC ORIG ID:XXXXXX8050 DESC DATE:SD0937 CO ENTRY DESCR:EFSLLC SEC:CCD TRACE#:XXXXXXXX1224521 EED:260529 IND ID:XXXXXXXX00387 IND NAME:SHOW FREI GHT INC . TRN: XXXXXX4521 TC</t>
+  </si>
+  <si>
     <t>Total for Fuel</t>
   </si>
   <si>
@@ -445,6 +457,15 @@
   </si>
   <si>
     <t>ORIG CO NAME:TRIUMPH INSURANC ORIG ID:XXXXXX9830 DESC DATE:260507 CO ENTRY DESCR:PAYMENTS SEC:CCD TRACE#:XXXXXXXX4927186 EED:260508 IND ID:31223462 IND NAME:SHO W FREIGHT INC TRN: XXXXXX7186 TC</t>
+  </si>
+  <si>
+    <t>05/28/2026</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:Premium Finance ORIG ID:XXXXXX4550 DESC DATE: CO ENTRY DESCR:Payments SEC:CCD TRACE#:XXXXXXXX4781553 EED:260528 IND ID:1104 -XX8274 IND NAME:SHOW FR EIGHT INC TRN: XXXXXX1553 TC</t>
+  </si>
+  <si>
+    <t>PLAT BUS CHECKING (7165) - 1</t>
   </si>
   <si>
     <t>Total for SF Truck Insurance</t>
@@ -574,6 +595,9 @@
     <t>FSP*A STORAGE ON WHEE XXX-XXX-1300 NV 05/14</t>
   </si>
   <si>
+    <t>ONLINE DOMESTIC WIRE TRANSFER VIA: WELLS FARGO NA/XXXXX0248 A/C: LJD ENTERPRISE LAS VEGAS NV X9102 US REF: TROP LOT/TIME/21:21 IMAD: 0528MMQFMP2MXX8477 TRN: 382 XXX6148ES 05/28</t>
+  </si>
+  <si>
     <t>Total for Storage/Parking</t>
   </si>
   <si>
@@ -746,9 +770,6 @@
     <t>Online RealTime vendor payment XXXXXXX2920 Payment Id REFERENCE#: XXXXXX2920RX to McKinney Vehicle Services Inc 3889</t>
   </si>
   <si>
-    <t>PLAT BUS CHECKING (7165) - 1</t>
-  </si>
-  <si>
     <t>04/27/2026</t>
   </si>
   <si>
@@ -816,6 +837,18 @@
   </si>
   <si>
     <t>ONLINE DOMESTIC WIRE TRANSFER VIA: HUNT COL/XXXXX0024 A/C: STAR LEASING COMPANY LLC CLEVELAND OH X4101 US REF: XXXX2990, XXXX4336, XXXX0217, XXXX1982 IMAD: 0521 MMQFMP2MXX5700 TRN: XXXXXX6141 ES 05/21</t>
+  </si>
+  <si>
+    <t>Online RealTime vendor payment XXXXXXX6695 Payment Id REFERENCE#: XXXXXX6695RX to McKinney Vehicle Services Inc 3889</t>
+  </si>
+  <si>
+    <t>05/27/2026</t>
+  </si>
+  <si>
+    <t>ONLINE DOMESTIC WIRE TRANSFER VIA: WELLS FARGO NA/XXXXX0248 A/C: UTILITY TRAILER SALES OF UTAH INC SALT LAKE CITY UT X4111 US REF: ACC XX4278 &amp; XX3803/TIME/08:0 1 IMAD: 0527MMQFMP2NXX1901 TRN: XXXXXX6147 ES 05/27</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:Ryder Truck Rent ORIG ID:XXXXXX7035 DESC DATE: CO ENTRY DESCR:EDI PYMNTSSEC:CCD TRACE#:XXXXXXXX1924536 EED:260527 IND ID:XXXXXX4338 IND NAME:SHOW F REIGHT INC EDI TRN: XXXXXX4536 TC</t>
   </si>
   <si>
     <t>Total for Trailer Rentals</t>
@@ -1071,6 +1104,18 @@
     <t>Online RealTime vendor payment XXXXXXX5272 Payment Id REFERENCE#: XXXXXX5272RX to TCI 3525</t>
   </si>
   <si>
+    <t>Online RealTime vendor payment XXXXXXX6225 Payment Id REFERENCE#: XXXXXX6225RX to TCI 3525</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:TRANSCO LEASING ORIG ID:XXXXXX3564 DESC DATE: CO ENTRY DESCR:ACH Pull SEC:CCD TRACE#:XXXXXXXX4660341 EED:260526 IND ID:10002608 IND NAME:Show Freig ht, Inc. 05/25/26 balance due\ TRN: XXXXXX0341 TC</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:Ryder Truck Rent ORIG ID:XXXXXX7035 DESC DATE: CO ENTRY DESCR:EDI PYMNTSSEC:CCD TRACE#:XXXXXXXX1924554 EED:260527 IND ID:XXXXXX5707 IND NAME:SHOW F REIGHT INC EDI TRN: XXXXXX4554 TC</t>
+  </si>
+  <si>
+    <t>ORIG CO NAME:Ryder Truck Rent ORIG ID:XXXXXX7035 DESC DATE: CO ENTRY DESCR:EDI PYMNTSSEC:CCD TRACE#:XXXXXXXX1924552 EED:260527 IND ID:XXXXXX6816 IND NAME:SHOW F REIGHT INC EDI TRN: XXXXXX4552 TC</t>
+  </si>
+  <si>
     <t>Total for Truck Rentals</t>
   </si>
   <si>
@@ -1155,7 +1200,7 @@
     <t>Balance</t>
   </si>
   <si>
-    <t>Accrual Basis Tuesday, May 26, 2026 01:02 AM GMTZ</t>
+    <t>Accrual Basis Saturday, May 30, 2026 04:44 PM GMTZ</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="35.875" style="26" customWidth="1"/>
@@ -1823,31 +1868,31 @@
     </row>
     <row r="5" spans="2:10" ht="16">
       <c r="B5" s="27" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="16">
@@ -3310,87 +3355,87 @@
         <v>467943.81</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="16">
-      <c r="A58" s="35" t="s">
+    <row r="58" spans="2:10" ht="16">
+      <c r="B58" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I58" s="29">
-        <f>I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29+I30+I31+I32+I33+I34+I35+I36+I37+I38+I39+I40+I41+I42+I43+I44+I45+I46+I47+I48+I49+I50+I51+I52+I53+I54+I55+I56+I57</f>
-        <v>467943.81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="16">
-      <c r="A59" s="34" t="s">
+      <c r="C58" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="25" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="60" spans="2:10" ht="16">
-      <c r="B60" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="25" t="s">
+      <c r="G58" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="28">
+        <v>13930.81</v>
+      </c>
+      <c r="J58" s="28">
+        <v>481874.62</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="16">
+      <c r="B59" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="C59" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="25" t="s">
+      <c r="G59" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="28">
+        <v>16710.61</v>
+      </c>
+      <c r="J59" s="28">
+        <v>498585.23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="16">
+      <c r="A60" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I60" s="28">
-        <v>6375.0</v>
-      </c>
-      <c r="J60" s="28">
-        <v>6375.0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="16">
-      <c r="B61" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="D61" s="25" t="s">
+      <c r="I60" s="29">
+        <f>I7+I8+I9+I10+I11+I12+I13+I14+I15+I16+I17+I18+I19+I20+I21+I22+I23+I24+I25+I26+I27+I28+I29+I30+I31+I32+I33+I34+I35+I36+I37+I38+I39+I40+I41+I42+I43+I44+I45+I46+I47+I48+I49+I50+I51+I52+I53+I54+I55+I56+I57+I58+I59</f>
+        <v>498585.23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="16">
+      <c r="A61" s="34" t="s">
         <v>117</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G61" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="H61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I61" s="28">
-        <v>6375.0</v>
-      </c>
-      <c r="J61" s="28">
-        <v>12750.0</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="16">
       <c r="B62" s="25" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C62" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E62" s="25" t="s">
         <v>7</v>
@@ -3399,7 +3444,7 @@
         <v>7</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H62" s="25" t="s">
         <v>7</v>
@@ -3408,18 +3453,18 @@
         <v>6375.0</v>
       </c>
       <c r="J62" s="28">
-        <v>19125.0</v>
+        <v>6375.0</v>
       </c>
     </row>
     <row r="63" spans="2:10" ht="16">
       <c r="B63" s="25" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E63" s="25" t="s">
         <v>7</v>
@@ -3428,7 +3473,7 @@
         <v>7</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H63" s="25" t="s">
         <v>7</v>
@@ -3437,27 +3482,27 @@
         <v>6375.0</v>
       </c>
       <c r="J63" s="28">
-        <v>25500.0</v>
+        <v>12750.0</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="16">
       <c r="B64" s="25" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D64" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="25" t="s">
         <v>120</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>116</v>
       </c>
       <c r="H64" s="25" t="s">
         <v>7</v>
@@ -3466,18 +3511,18 @@
         <v>6375.0</v>
       </c>
       <c r="J64" s="28">
-        <v>31875.0</v>
+        <v>19125.0</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="16">
       <c r="B65" s="25" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E65" s="25" t="s">
         <v>7</v>
@@ -3486,7 +3531,7 @@
         <v>7</v>
       </c>
       <c r="G65" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H65" s="25" t="s">
         <v>7</v>
@@ -3495,18 +3540,18 @@
         <v>6375.0</v>
       </c>
       <c r="J65" s="28">
-        <v>38250.0</v>
+        <v>25500.0</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="16">
       <c r="B66" s="25" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E66" s="25" t="s">
         <v>7</v>
@@ -3515,7 +3560,7 @@
         <v>7</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H66" s="25" t="s">
         <v>7</v>
@@ -3524,18 +3569,18 @@
         <v>6375.0</v>
       </c>
       <c r="J66" s="28">
-        <v>44625.0</v>
+        <v>31875.0</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="16">
       <c r="B67" s="25" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E67" s="25" t="s">
         <v>7</v>
@@ -3544,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H67" s="25" t="s">
         <v>7</v>
@@ -3553,18 +3598,18 @@
         <v>6375.0</v>
       </c>
       <c r="J67" s="28">
-        <v>51000.0</v>
+        <v>38250.0</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="16">
       <c r="B68" s="25" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C68" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E68" s="25" t="s">
         <v>7</v>
@@ -3573,7 +3618,7 @@
         <v>7</v>
       </c>
       <c r="G68" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H68" s="25" t="s">
         <v>7</v>
@@ -3582,44 +3627,44 @@
         <v>6375.0</v>
       </c>
       <c r="J68" s="28">
-        <v>57375.0</v>
+        <v>44625.0</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="16">
       <c r="B69" s="25" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="C69" s="25" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="G69" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H69" s="25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I69" s="28">
-        <v>467.44</v>
+        <v>6375.0</v>
       </c>
       <c r="J69" s="28">
-        <v>57842.44</v>
+        <v>51000.0</v>
       </c>
     </row>
     <row r="70" spans="2:10" ht="16">
       <c r="B70" s="25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D70" s="25" t="s">
         <v>128</v>
@@ -3631,7 +3676,7 @@
         <v>7</v>
       </c>
       <c r="G70" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H70" s="25" t="s">
         <v>7</v>
@@ -3640,47 +3685,47 @@
         <v>6375.0</v>
       </c>
       <c r="J70" s="28">
-        <v>64217.44</v>
+        <v>57375.0</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="16">
       <c r="B71" s="25" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>114</v>
+        <v>6</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="G71" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H71" s="25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I71" s="28">
-        <v>6375.0</v>
+        <v>467.44</v>
       </c>
       <c r="J71" s="28">
-        <v>70592.44</v>
+        <v>57842.44</v>
       </c>
     </row>
     <row r="72" spans="2:10" ht="16">
       <c r="B72" s="25" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C72" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E72" s="25" t="s">
         <v>7</v>
@@ -3689,7 +3734,7 @@
         <v>7</v>
       </c>
       <c r="G72" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H72" s="25" t="s">
         <v>7</v>
@@ -3698,171 +3743,215 @@
         <v>6375.0</v>
       </c>
       <c r="J72" s="28">
-        <v>76967.44</v>
+        <v>64217.44</v>
       </c>
     </row>
     <row r="73" spans="2:10" ht="16">
       <c r="B73" s="25" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H73" s="25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I73" s="28">
-        <v>7236.0</v>
+        <v>6375.0</v>
       </c>
       <c r="J73" s="28">
-        <v>84203.44</v>
+        <v>70592.44</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="16">
       <c r="B74" s="25" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="G74" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="I74" s="28">
-        <v>18641.8</v>
+        <v>6375.0</v>
       </c>
       <c r="J74" s="28">
-        <v>102845.24</v>
+        <v>76967.44</v>
       </c>
     </row>
     <row r="75" spans="2:10" ht="16">
       <c r="B75" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C75" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="F75" s="25" t="s">
-        <v>136</v>
-      </c>
       <c r="G75" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I75" s="28">
-        <v>2291.04</v>
+        <v>7236.0</v>
       </c>
       <c r="J75" s="28">
-        <v>105136.28</v>
+        <v>84203.44</v>
       </c>
     </row>
     <row r="76" spans="2:10" ht="16">
       <c r="B76" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F76" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C76" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="F76" s="25" t="s">
+      <c r="G76" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H76" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="G76" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="H76" s="25" t="s">
-        <v>134</v>
-      </c>
       <c r="I76" s="28">
-        <v>19054.42</v>
+        <v>18641.8</v>
       </c>
       <c r="J76" s="28">
-        <v>124190.7</v>
+        <v>102845.24</v>
       </c>
     </row>
     <row r="77" spans="2:10" ht="16">
       <c r="B77" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F77" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G77" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H77" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I77" s="28">
+        <v>2291.04</v>
+      </c>
+      <c r="J77" s="28">
+        <v>105136.28</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="16">
+      <c r="B78" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="G78" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H78" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I78" s="28">
+        <v>19054.42</v>
+      </c>
+      <c r="J78" s="28">
+        <v>124190.7</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="16">
+      <c r="B79" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C77" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="G77" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="H77" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="I77" s="28">
+      <c r="C79" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G79" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H79" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I79" s="28">
         <v>4433.75</v>
       </c>
-      <c r="J77" s="28">
+      <c r="J79" s="28">
         <v>128624.45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="16">
-      <c r="A78" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I78" s="29">
-        <f>I59+I60+I61+I62+I63+I64+I65+I66+I67+I68+I69+I70+I71+I72+I73+I74+I75+I76+I77</f>
-        <v>128624.45</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" ht="16">
-      <c r="A79" s="34" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="80" spans="2:10" ht="16">
       <c r="B80" s="25" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="C80" s="25" t="s">
         <v>6</v>
@@ -3871,114 +3960,70 @@
         <v>7</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G80" s="25" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H80" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I80" s="28">
-        <v>3100.0</v>
+        <v>19054.42</v>
       </c>
       <c r="J80" s="28">
-        <v>3100.0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="16">
-      <c r="B81" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="F81" s="25" t="s">
+        <v>147678.87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="16">
+      <c r="A81" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="G81" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="H81" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I81" s="28">
-        <v>270.94</v>
-      </c>
-      <c r="J81" s="28">
-        <v>3370.94</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="16">
-      <c r="B82" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="F82" s="25" t="s">
+      <c r="I81" s="29">
+        <f>I61+I62+I63+I64+I65+I66+I67+I68+I69+I70+I71+I72+I73+I74+I75+I76+I77+I78+I79+I80</f>
+        <v>147678.87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="16">
+      <c r="A82" s="34" t="s">
         <v>148</v>
-      </c>
-      <c r="G82" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="H82" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I82" s="28">
-        <v>97.54</v>
-      </c>
-      <c r="J82" s="28">
-        <v>3468.48</v>
       </c>
     </row>
     <row r="83" spans="2:10" ht="16">
       <c r="B83" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" s="25" t="s">
         <v>149</v>
-      </c>
-      <c r="C83" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="25" t="s">
-        <v>142</v>
       </c>
       <c r="F83" s="25" t="s">
         <v>150</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H83" s="25" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I83" s="28">
         <v>3100.0</v>
       </c>
       <c r="J83" s="28">
-        <v>6568.48</v>
+        <v>3100.0</v>
       </c>
     </row>
     <row r="84" spans="2:10" ht="16">
       <c r="B84" s="25" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="C84" s="25" t="s">
         <v>6</v>
@@ -3987,56 +4032,56 @@
         <v>7</v>
       </c>
       <c r="E84" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="F84" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G84" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="F84" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="G84" s="25" t="s">
-        <v>144</v>
-      </c>
       <c r="H84" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I84" s="28">
-        <v>105.95</v>
+        <v>270.94</v>
       </c>
       <c r="J84" s="28">
-        <v>6674.429999999999</v>
+        <v>3370.94</v>
       </c>
     </row>
     <row r="85" spans="2:10" ht="16">
       <c r="B85" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="C85" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="25" t="s">
-        <v>146</v>
-      </c>
       <c r="F85" s="25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G85" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H85" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I85" s="28">
-        <v>270.94</v>
+        <v>97.54</v>
       </c>
       <c r="J85" s="28">
-        <v>6945.369999999999</v>
+        <v>3468.48</v>
       </c>
     </row>
     <row r="86" spans="2:10" ht="16">
       <c r="B86" s="25" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="C86" s="25" t="s">
         <v>6</v>
@@ -4045,22 +4090,22 @@
         <v>7</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H86" s="25" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="I86" s="28">
-        <v>97.54</v>
+        <v>3100.0</v>
       </c>
       <c r="J86" s="28">
-        <v>7042.909999999999</v>
+        <v>6568.48</v>
       </c>
     </row>
     <row r="87" spans="2:10" ht="16">
@@ -4074,27 +4119,27 @@
         <v>7</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G87" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H87" s="25" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="I87" s="28">
-        <v>3100.0</v>
+        <v>105.95</v>
       </c>
       <c r="J87" s="28">
-        <v>10142.91</v>
+        <v>6674.429999999999</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="16">
       <c r="B88" s="25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C88" s="25" t="s">
         <v>6</v>
@@ -4103,13 +4148,13 @@
         <v>7</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G88" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H88" s="25" t="s">
         <v>11</v>
@@ -4118,12 +4163,12 @@
         <v>270.94</v>
       </c>
       <c r="J88" s="28">
-        <v>10413.85</v>
+        <v>6945.369999999999</v>
       </c>
     </row>
     <row r="89" spans="2:10" ht="16">
       <c r="B89" s="25" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C89" s="25" t="s">
         <v>6</v>
@@ -4132,27 +4177,27 @@
         <v>7</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G89" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H89" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I89" s="28">
-        <v>203.5</v>
+        <v>97.54</v>
       </c>
       <c r="J89" s="28">
-        <v>10617.35</v>
+        <v>7042.909999999999</v>
       </c>
     </row>
     <row r="90" spans="2:10" ht="16">
       <c r="B90" s="25" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="C90" s="25" t="s">
         <v>6</v>
@@ -4161,27 +4206,27 @@
         <v>7</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G90" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H90" s="25" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="I90" s="28">
-        <v>105.0</v>
+        <v>3100.0</v>
       </c>
       <c r="J90" s="28">
-        <v>10722.35</v>
+        <v>10142.91</v>
       </c>
     </row>
     <row r="91" spans="2:10" ht="16">
       <c r="B91" s="25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C91" s="25" t="s">
         <v>6</v>
@@ -4190,27 +4235,27 @@
         <v>7</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="I91" s="28">
-        <v>3100.0</v>
+        <v>270.94</v>
       </c>
       <c r="J91" s="28">
-        <v>13822.35</v>
+        <v>10413.85</v>
       </c>
     </row>
     <row r="92" spans="2:10" ht="16">
       <c r="B92" s="25" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C92" s="25" t="s">
         <v>6</v>
@@ -4219,27 +4264,27 @@
         <v>7</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G92" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H92" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I92" s="28">
-        <v>58.61</v>
+        <v>203.5</v>
       </c>
       <c r="J92" s="28">
-        <v>13880.960000000001</v>
+        <v>10617.35</v>
       </c>
     </row>
     <row r="93" spans="2:10" ht="16">
       <c r="B93" s="25" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C93" s="25" t="s">
         <v>6</v>
@@ -4248,27 +4293,27 @@
         <v>7</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G93" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H93" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I93" s="28">
-        <v>270.94</v>
+        <v>105.0</v>
       </c>
       <c r="J93" s="28">
-        <v>14151.900000000001</v>
+        <v>10722.35</v>
       </c>
     </row>
     <row r="94" spans="2:10" ht="16">
       <c r="B94" s="25" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C94" s="25" t="s">
         <v>6</v>
@@ -4277,27 +4322,27 @@
         <v>7</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="I94" s="28">
-        <v>775.0</v>
+        <v>3100.0</v>
       </c>
       <c r="J94" s="28">
-        <v>14926.900000000001</v>
+        <v>13822.35</v>
       </c>
     </row>
     <row r="95" spans="2:10" ht="16">
       <c r="B95" s="25" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C95" s="25" t="s">
         <v>6</v>
@@ -4306,27 +4351,27 @@
         <v>7</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H95" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I95" s="28">
-        <v>775.0</v>
+        <v>58.61</v>
       </c>
       <c r="J95" s="28">
-        <v>15701.900000000001</v>
+        <v>13880.960000000001</v>
       </c>
     </row>
     <row r="96" spans="2:10" ht="16">
       <c r="B96" s="25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C96" s="25" t="s">
         <v>6</v>
@@ -4335,27 +4380,27 @@
         <v>7</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H96" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I96" s="28">
-        <v>216.78</v>
+        <v>270.94</v>
       </c>
       <c r="J96" s="28">
-        <v>15918.680000000002</v>
+        <v>14151.900000000001</v>
       </c>
     </row>
     <row r="97" spans="2:10" ht="16">
       <c r="B97" s="25" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="C97" s="25" t="s">
         <v>6</v>
@@ -4364,27 +4409,27 @@
         <v>7</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H97" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I97" s="28">
-        <v>10000.0</v>
+        <v>775.0</v>
       </c>
       <c r="J97" s="28">
-        <v>25918.68</v>
+        <v>14926.900000000001</v>
       </c>
     </row>
     <row r="98" spans="2:10" ht="16">
       <c r="B98" s="25" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="C98" s="25" t="s">
         <v>6</v>
@@ -4393,13 +4438,13 @@
         <v>7</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F98" s="25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H98" s="25" t="s">
         <v>11</v>
@@ -4408,12 +4453,12 @@
         <v>775.0</v>
       </c>
       <c r="J98" s="28">
-        <v>26693.68</v>
+        <v>15701.900000000001</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="16">
       <c r="B99" s="25" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="C99" s="25" t="s">
         <v>6</v>
@@ -4422,27 +4467,27 @@
         <v>7</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G99" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H99" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I99" s="28">
-        <v>775.0</v>
+        <v>216.78</v>
       </c>
       <c r="J99" s="28">
-        <v>27468.68</v>
+        <v>15918.680000000002</v>
       </c>
     </row>
     <row r="100" spans="2:10" ht="16">
       <c r="B100" s="25" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="C100" s="25" t="s">
         <v>6</v>
@@ -4451,27 +4496,27 @@
         <v>7</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G100" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H100" s="25" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="I100" s="28">
-        <v>3100.0</v>
+        <v>10000.0</v>
       </c>
       <c r="J100" s="28">
-        <v>30568.68</v>
+        <v>25918.68</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="16">
       <c r="B101" s="25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C101" s="25" t="s">
         <v>6</v>
@@ -4480,41 +4525,85 @@
         <v>7</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F101" s="25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G101" s="25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H101" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I101" s="28">
-        <v>270.94</v>
+        <v>775.0</v>
       </c>
       <c r="J101" s="28">
-        <v>30839.62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="16">
-      <c r="A102" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="I102" s="29">
-        <f>I79+I80+I81+I82+I83+I84+I85+I86+I87+I88+I89+I90+I91+I92+I93+I94+I95+I96+I97+I98+I99+I100+I101</f>
-        <v>30839.62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" ht="16">
-      <c r="A103" s="34" t="s">
-        <v>183</v>
+        <v>26693.68</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="16">
+      <c r="B102" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F102" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G102" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H102" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="28">
+        <v>775.0</v>
+      </c>
+      <c r="J102" s="28">
+        <v>27468.68</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="16">
+      <c r="B103" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F103" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="G103" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H103" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I103" s="28">
+        <v>3100.0</v>
+      </c>
+      <c r="J103" s="28">
+        <v>30568.68</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="16">
       <c r="B104" s="25" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="C104" s="25" t="s">
         <v>6</v>
@@ -4523,27 +4612,27 @@
         <v>7</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="H104" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I104" s="28">
-        <v>3734.48</v>
+        <v>270.94</v>
       </c>
       <c r="J104" s="28">
-        <v>3734.48</v>
+        <v>30839.62</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="16">
       <c r="B105" s="25" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="C105" s="25" t="s">
         <v>6</v>
@@ -4552,85 +4641,41 @@
         <v>7</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G105" s="25" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="H105" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I105" s="28">
-        <v>405.23</v>
+        <v>8550.0</v>
       </c>
       <c r="J105" s="28">
-        <v>4139.71</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" ht="16">
-      <c r="B106" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C106" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D106" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E106" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="F106" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="G106" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="H106" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I106" s="28">
-        <v>452.18</v>
-      </c>
-      <c r="J106" s="28">
-        <v>4591.89</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" ht="16">
-      <c r="B107" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C107" s="25" t="s">
+        <v>39389.619999999995</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="16">
+      <c r="A106" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="D107" s="25" t="s">
+      <c r="I106" s="29">
+        <f>I82+I83+I84+I85+I86+I87+I88+I89+I90+I91+I92+I93+I94+I95+I96+I97+I98+I99+I100+I101+I102+I103+I104+I105</f>
+        <v>39389.619999999995</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="16">
+      <c r="A107" s="34" t="s">
         <v>191</v>
-      </c>
-      <c r="E107" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="G107" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="H107" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I107" s="28">
-        <v>-750.0</v>
-      </c>
-      <c r="J107" s="28">
-        <v>3841.8900000000003</v>
       </c>
     </row>
     <row r="108" spans="2:10" ht="16">
       <c r="B108" s="25" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>6</v>
@@ -4639,70 +4684,114 @@
         <v>7</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F108" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="G108" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="G108" s="25" t="s">
-        <v>186</v>
-      </c>
       <c r="H108" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I108" s="28">
-        <v>568.15</v>
+        <v>3734.48</v>
       </c>
       <c r="J108" s="28">
-        <v>4410.04</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="16">
-      <c r="A109" s="35" t="s">
+        <v>3734.48</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" ht="16">
+      <c r="B109" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="I109" s="29">
-        <f>I103+I104+I105+I106+I107+I108</f>
-        <v>4410.04</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="16">
-      <c r="A110" s="34" t="s">
+      <c r="F109" s="25" t="s">
         <v>196</v>
+      </c>
+      <c r="G109" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="H109" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I109" s="28">
+        <v>405.23</v>
+      </c>
+      <c r="J109" s="28">
+        <v>4139.71</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" ht="16">
+      <c r="B110" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="G110" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="H110" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I110" s="28">
+        <v>452.18</v>
+      </c>
+      <c r="J110" s="28">
+        <v>4591.89</v>
       </c>
     </row>
     <row r="111" spans="2:10" ht="16">
       <c r="B111" s="25" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>7</v>
+        <v>199</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F111" s="25" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G111" s="25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H111" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I111" s="28">
-        <v>2520.0</v>
+        <v>-750.0</v>
       </c>
       <c r="J111" s="28">
-        <v>2520.0</v>
+        <v>3841.8900000000003</v>
       </c>
     </row>
     <row r="112" spans="2:10" ht="16">
       <c r="B112" s="25" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>6</v>
@@ -4711,85 +4800,41 @@
         <v>7</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F112" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G112" s="25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H112" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I112" s="28">
-        <v>876.73</v>
+        <v>568.15</v>
       </c>
       <c r="J112" s="28">
-        <v>3396.73</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" ht="16">
-      <c r="B113" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="C113" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D113" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E113" s="25" t="s">
+        <v>4410.04</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="16">
+      <c r="A113" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="I113" s="29">
+        <f>I107+I108+I109+I110+I111+I112</f>
+        <v>4410.04</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="16">
+      <c r="A114" s="34" t="s">
         <v>204</v>
-      </c>
-      <c r="G113" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="H113" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I113" s="28">
-        <v>4222.31</v>
-      </c>
-      <c r="J113" s="28">
-        <v>7619.040000000001</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" ht="16">
-      <c r="B114" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C114" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D114" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E114" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="F114" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="G114" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="H114" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I114" s="28">
-        <v>2000.0</v>
-      </c>
-      <c r="J114" s="28">
-        <v>9619.04</v>
       </c>
     </row>
     <row r="115" spans="2:10" ht="16">
       <c r="B115" s="25" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C115" s="25" t="s">
         <v>6</v>
@@ -4801,24 +4846,24 @@
         <v>205</v>
       </c>
       <c r="F115" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="G115" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="G115" s="25" t="s">
-        <v>199</v>
-      </c>
       <c r="H115" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I115" s="28">
-        <v>2000.0</v>
+        <v>2520.0</v>
       </c>
       <c r="J115" s="28">
-        <v>11619.04</v>
+        <v>2520.0</v>
       </c>
     </row>
     <row r="116" spans="2:10" ht="16">
       <c r="B116" s="25" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C116" s="25" t="s">
         <v>6</v>
@@ -4827,27 +4872,27 @@
         <v>7</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F116" s="25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G116" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H116" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I116" s="28">
-        <v>2520.0</v>
+        <v>876.73</v>
       </c>
       <c r="J116" s="28">
-        <v>14139.04</v>
+        <v>3396.73</v>
       </c>
     </row>
     <row r="117" spans="2:10" ht="16">
       <c r="B117" s="25" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="C117" s="25" t="s">
         <v>6</v>
@@ -4856,27 +4901,27 @@
         <v>7</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F117" s="25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H117" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I117" s="28">
-        <v>2000.0</v>
+        <v>4222.31</v>
       </c>
       <c r="J117" s="28">
-        <v>16139.04</v>
+        <v>7619.040000000001</v>
       </c>
     </row>
     <row r="118" spans="2:10" ht="16">
       <c r="B118" s="25" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>6</v>
@@ -4885,13 +4930,13 @@
         <v>7</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G118" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H118" s="25" t="s">
         <v>11</v>
@@ -4900,12 +4945,12 @@
         <v>2000.0</v>
       </c>
       <c r="J118" s="28">
-        <v>18139.04</v>
+        <v>9619.04</v>
       </c>
     </row>
     <row r="119" spans="2:10" ht="16">
       <c r="B119" s="25" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="C119" s="25" t="s">
         <v>6</v>
@@ -4914,27 +4959,27 @@
         <v>7</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F119" s="25" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G119" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H119" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I119" s="28">
-        <v>4000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="J119" s="28">
-        <v>22139.04</v>
+        <v>11619.04</v>
       </c>
     </row>
     <row r="120" spans="2:10" ht="16">
       <c r="B120" s="25" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C120" s="25" t="s">
         <v>6</v>
@@ -4946,24 +4991,24 @@
         <v>205</v>
       </c>
       <c r="F120" s="25" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G120" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H120" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I120" s="28">
-        <v>5137.31</v>
+        <v>2520.0</v>
       </c>
       <c r="J120" s="28">
-        <v>27276.350000000002</v>
+        <v>14139.04</v>
       </c>
     </row>
     <row r="121" spans="2:10" ht="16">
       <c r="B121" s="25" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C121" s="25" t="s">
         <v>6</v>
@@ -4972,27 +5017,27 @@
         <v>7</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F121" s="25" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G121" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H121" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I121" s="28">
-        <v>1638.99</v>
+        <v>2000.0</v>
       </c>
       <c r="J121" s="28">
-        <v>28915.340000000004</v>
+        <v>16139.04</v>
       </c>
     </row>
     <row r="122" spans="2:10" ht="16">
       <c r="B122" s="25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C122" s="25" t="s">
         <v>6</v>
@@ -5001,27 +5046,27 @@
         <v>7</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F122" s="25" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G122" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H122" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I122" s="28">
-        <v>2520.0</v>
+        <v>2000.0</v>
       </c>
       <c r="J122" s="28">
-        <v>31435.340000000004</v>
+        <v>18139.04</v>
       </c>
     </row>
     <row r="123" spans="2:10" ht="16">
       <c r="B123" s="25" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C123" s="25" t="s">
         <v>6</v>
@@ -5030,27 +5075,27 @@
         <v>7</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F123" s="25" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G123" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H123" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I123" s="28">
-        <v>6238.26</v>
+        <v>4000.0</v>
       </c>
       <c r="J123" s="28">
-        <v>37673.600000000006</v>
+        <v>22139.04</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="16">
       <c r="B124" s="25" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C124" s="25" t="s">
         <v>6</v>
@@ -5059,27 +5104,27 @@
         <v>7</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F124" s="25" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G124" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H124" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I124" s="28">
-        <v>10888.77</v>
+        <v>5137.31</v>
       </c>
       <c r="J124" s="28">
-        <v>48562.37000000001</v>
+        <v>27276.350000000002</v>
       </c>
     </row>
     <row r="125" spans="2:10" ht="16">
       <c r="B125" s="25" t="s">
-        <v>219</v>
+        <v>52</v>
       </c>
       <c r="C125" s="25" t="s">
         <v>6</v>
@@ -5088,27 +5133,27 @@
         <v>7</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F125" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G125" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H125" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I125" s="28">
-        <v>1141.55</v>
+        <v>1638.99</v>
       </c>
       <c r="J125" s="28">
-        <v>49703.92000000001</v>
+        <v>28915.340000000004</v>
       </c>
     </row>
     <row r="126" spans="2:10" ht="16">
       <c r="B126" s="25" t="s">
-        <v>221</v>
+        <v>52</v>
       </c>
       <c r="C126" s="25" t="s">
         <v>6</v>
@@ -5117,22 +5162,22 @@
         <v>7</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="F126" s="25" t="s">
         <v>223</v>
       </c>
       <c r="G126" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H126" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I126" s="28">
-        <v>1402.12</v>
+        <v>2520.0</v>
       </c>
       <c r="J126" s="28">
-        <v>51106.040000000015</v>
+        <v>31435.340000000004</v>
       </c>
     </row>
     <row r="127" spans="2:10" ht="16">
@@ -5146,56 +5191,56 @@
         <v>7</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F127" s="25" t="s">
         <v>225</v>
       </c>
       <c r="G127" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H127" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I127" s="28">
-        <v>12189.24</v>
+        <v>6238.26</v>
       </c>
       <c r="J127" s="28">
-        <v>63295.28000000001</v>
+        <v>37673.600000000006</v>
       </c>
     </row>
     <row r="128" spans="2:10" ht="16">
       <c r="B128" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E128" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="F128" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="C128" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D128" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E128" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="F128" s="25" t="s">
-        <v>227</v>
-      </c>
       <c r="G128" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H128" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I128" s="28">
-        <v>5362.39</v>
+        <v>10888.77</v>
       </c>
       <c r="J128" s="28">
-        <v>68657.67000000001</v>
+        <v>48562.37000000001</v>
       </c>
     </row>
     <row r="129" spans="2:10" ht="16">
       <c r="B129" s="25" t="s">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="C129" s="25" t="s">
         <v>6</v>
@@ -5204,56 +5249,56 @@
         <v>7</v>
       </c>
       <c r="E129" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F129" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="F129" s="25" t="s">
-        <v>229</v>
-      </c>
       <c r="G129" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H129" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I129" s="28">
-        <v>2171.98</v>
+        <v>1141.55</v>
       </c>
       <c r="J129" s="28">
-        <v>70829.65000000001</v>
+        <v>49703.92000000001</v>
       </c>
     </row>
     <row r="130" spans="2:10" ht="16">
       <c r="B130" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" s="25" t="s">
         <v>230</v>
-      </c>
-      <c r="C130" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D130" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E130" s="25" t="s">
-        <v>205</v>
       </c>
       <c r="F130" s="25" t="s">
         <v>231</v>
       </c>
       <c r="G130" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H130" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I130" s="28">
-        <v>2455.03</v>
+        <v>1402.12</v>
       </c>
       <c r="J130" s="28">
-        <v>73284.68000000001</v>
+        <v>51106.040000000015</v>
       </c>
     </row>
     <row r="131" spans="2:10" ht="16">
       <c r="B131" s="25" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="C131" s="25" t="s">
         <v>6</v>
@@ -5262,27 +5307,27 @@
         <v>7</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F131" s="25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G131" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H131" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I131" s="28">
-        <v>2574.9</v>
+        <v>12189.24</v>
       </c>
       <c r="J131" s="28">
-        <v>75859.58</v>
+        <v>63295.28000000001</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="16">
       <c r="B132" s="25" t="s">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="C132" s="25" t="s">
         <v>6</v>
@@ -5291,27 +5336,27 @@
         <v>7</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F132" s="25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G132" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H132" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I132" s="28">
-        <v>3000.0</v>
+        <v>5362.39</v>
       </c>
       <c r="J132" s="28">
-        <v>78859.58</v>
+        <v>68657.67000000001</v>
       </c>
     </row>
     <row r="133" spans="2:10" ht="16">
       <c r="B133" s="25" t="s">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="C133" s="25" t="s">
         <v>6</v>
@@ -5320,27 +5365,27 @@
         <v>7</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F133" s="25" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G133" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H133" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I133" s="28">
-        <v>1754.1</v>
+        <v>2171.98</v>
       </c>
       <c r="J133" s="28">
-        <v>80613.68000000001</v>
+        <v>70829.65000000001</v>
       </c>
     </row>
     <row r="134" spans="2:10" ht="16">
       <c r="B134" s="25" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C134" s="25" t="s">
         <v>6</v>
@@ -5349,27 +5394,27 @@
         <v>7</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F134" s="25" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G134" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H134" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I134" s="28">
-        <v>889.76</v>
+        <v>2455.03</v>
       </c>
       <c r="J134" s="28">
-        <v>81503.44</v>
+        <v>73284.68000000001</v>
       </c>
     </row>
     <row r="135" spans="2:10" ht="16">
       <c r="B135" s="25" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C135" s="25" t="s">
         <v>6</v>
@@ -5378,27 +5423,27 @@
         <v>7</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F135" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G135" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H135" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I135" s="28">
-        <v>6000.0</v>
+        <v>2574.9</v>
       </c>
       <c r="J135" s="28">
-        <v>87503.44</v>
+        <v>75859.58</v>
       </c>
     </row>
     <row r="136" spans="2:10" ht="16">
       <c r="B136" s="25" t="s">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="C136" s="25" t="s">
         <v>6</v>
@@ -5410,24 +5455,24 @@
         <v>205</v>
       </c>
       <c r="F136" s="25" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G136" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H136" s="25" t="s">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="I136" s="28">
-        <v>6330.55</v>
+        <v>3000.0</v>
       </c>
       <c r="J136" s="28">
-        <v>93833.99</v>
+        <v>78859.58</v>
       </c>
     </row>
     <row r="137" spans="2:10" ht="16">
       <c r="B137" s="25" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="C137" s="25" t="s">
         <v>6</v>
@@ -5436,27 +5481,27 @@
         <v>7</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G137" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H137" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I137" s="28">
-        <v>3000.0</v>
+        <v>1754.1</v>
       </c>
       <c r="J137" s="28">
-        <v>96833.99</v>
+        <v>80613.68000000001</v>
       </c>
     </row>
     <row r="138" spans="2:10" ht="16">
       <c r="B138" s="25" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="C138" s="25" t="s">
         <v>6</v>
@@ -5465,27 +5510,27 @@
         <v>7</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G138" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H138" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I138" s="28">
-        <v>1883.29</v>
+        <v>889.76</v>
       </c>
       <c r="J138" s="28">
-        <v>98717.28</v>
+        <v>81503.44</v>
       </c>
     </row>
     <row r="139" spans="2:10" ht="16">
       <c r="B139" s="25" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="C139" s="25" t="s">
         <v>6</v>
@@ -5494,27 +5539,27 @@
         <v>7</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G139" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H139" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I139" s="28">
-        <v>1044.24</v>
+        <v>6000.0</v>
       </c>
       <c r="J139" s="28">
-        <v>99761.52</v>
+        <v>87503.44</v>
       </c>
     </row>
     <row r="140" spans="2:10" ht="16">
       <c r="B140" s="25" t="s">
-        <v>245</v>
+        <v>94</v>
       </c>
       <c r="C140" s="25" t="s">
         <v>6</v>
@@ -5523,27 +5568,27 @@
         <v>7</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F140" s="25" t="s">
         <v>246</v>
       </c>
       <c r="G140" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="I140" s="28">
-        <v>7363.61</v>
+        <v>6330.55</v>
       </c>
       <c r="J140" s="28">
-        <v>107125.13</v>
+        <v>93833.99</v>
       </c>
     </row>
     <row r="141" spans="2:10" ht="16">
       <c r="B141" s="25" t="s">
-        <v>98</v>
+        <v>247</v>
       </c>
       <c r="C141" s="25" t="s">
         <v>6</v>
@@ -5552,27 +5597,27 @@
         <v>7</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G141" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H141" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I141" s="28">
-        <v>3359.9</v>
+        <v>3000.0</v>
       </c>
       <c r="J141" s="28">
-        <v>110485.03</v>
+        <v>96833.99</v>
       </c>
     </row>
     <row r="142" spans="2:10" ht="16">
       <c r="B142" s="25" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C142" s="25" t="s">
         <v>6</v>
@@ -5581,27 +5626,27 @@
         <v>7</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G142" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H142" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I142" s="28">
-        <v>3561.36</v>
+        <v>1883.29</v>
       </c>
       <c r="J142" s="28">
-        <v>114046.39</v>
+        <v>98717.28</v>
       </c>
     </row>
     <row r="143" spans="2:10" ht="16">
       <c r="B143" s="25" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C143" s="25" t="s">
         <v>6</v>
@@ -5610,27 +5655,27 @@
         <v>7</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H143" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I143" s="28">
-        <v>2520.0</v>
+        <v>1044.24</v>
       </c>
       <c r="J143" s="28">
-        <v>116566.39</v>
+        <v>99761.52</v>
       </c>
     </row>
     <row r="144" spans="2:10" ht="16">
       <c r="B144" s="25" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C144" s="25" t="s">
         <v>6</v>
@@ -5639,27 +5684,27 @@
         <v>7</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F144" s="25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G144" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H144" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I144" s="28">
-        <v>3500.0</v>
+        <v>7363.61</v>
       </c>
       <c r="J144" s="28">
-        <v>120066.39</v>
+        <v>107125.13</v>
       </c>
     </row>
     <row r="145" spans="2:10" ht="16">
       <c r="B145" s="25" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C145" s="25" t="s">
         <v>6</v>
@@ -5668,27 +5713,27 @@
         <v>7</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G145" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H145" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I145" s="28">
-        <v>15000.0</v>
+        <v>3359.9</v>
       </c>
       <c r="J145" s="28">
-        <v>135066.39</v>
+        <v>110485.03</v>
       </c>
     </row>
     <row r="146" spans="2:10" ht="16">
       <c r="B146" s="25" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="C146" s="25" t="s">
         <v>6</v>
@@ -5697,27 +5742,27 @@
         <v>7</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F146" s="25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G146" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H146" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I146" s="28">
-        <v>2520.0</v>
+        <v>3561.36</v>
       </c>
       <c r="J146" s="28">
-        <v>137586.39</v>
+        <v>114046.39</v>
       </c>
     </row>
     <row r="147" spans="2:10" ht="16">
       <c r="B147" s="25" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="C147" s="25" t="s">
         <v>6</v>
@@ -5726,27 +5771,27 @@
         <v>7</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="F147" s="25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G147" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H147" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I147" s="28">
-        <v>1533.49</v>
+        <v>2520.0</v>
       </c>
       <c r="J147" s="28">
-        <v>139119.88</v>
+        <v>116566.39</v>
       </c>
     </row>
     <row r="148" spans="2:10" ht="16">
       <c r="B148" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C148" s="25" t="s">
         <v>6</v>
@@ -5755,27 +5800,27 @@
         <v>7</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F148" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G148" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H148" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I148" s="28">
-        <v>1139.84</v>
+        <v>3500.0</v>
       </c>
       <c r="J148" s="28">
-        <v>140259.72</v>
+        <v>120066.39</v>
       </c>
     </row>
     <row r="149" spans="2:10" ht="16">
       <c r="B149" s="25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C149" s="25" t="s">
         <v>6</v>
@@ -5784,27 +5829,27 @@
         <v>7</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G149" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I149" s="28">
-        <v>3684.33</v>
+        <v>15000.0</v>
       </c>
       <c r="J149" s="28">
-        <v>143944.05</v>
+        <v>135066.39</v>
       </c>
     </row>
     <row r="150" spans="2:10" ht="16">
       <c r="B150" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C150" s="25" t="s">
         <v>6</v>
@@ -5813,13 +5858,13 @@
         <v>7</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F150" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G150" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H150" s="25" t="s">
         <v>11</v>
@@ -5828,12 +5873,12 @@
         <v>2520.0</v>
       </c>
       <c r="J150" s="28">
-        <v>146464.05</v>
+        <v>137586.39</v>
       </c>
     </row>
     <row r="151" spans="2:10" ht="16">
       <c r="B151" s="25" t="s">
-        <v>261</v>
+        <v>106</v>
       </c>
       <c r="C151" s="25" t="s">
         <v>6</v>
@@ -5842,41 +5887,85 @@
         <v>7</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F151" s="25" t="s">
         <v>262</v>
       </c>
       <c r="G151" s="25" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H151" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I151" s="28">
-        <v>6138.58</v>
+        <v>1533.49</v>
       </c>
       <c r="J151" s="28">
-        <v>152602.62999999998</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="16">
-      <c r="A152" s="35" t="s">
+        <v>139119.88</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" ht="16">
+      <c r="B152" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="I152" s="29">
-        <f>I110+I111+I112+I113+I114+I115+I116+I117+I118+I119+I120+I121+I122+I123+I124+I125+I126+I127+I128+I129+I130+I131+I132+I133+I134+I135+I136+I137+I138+I139+I140+I141+I142+I143+I144+I145+I146+I147+I148+I149+I150+I151</f>
-        <v>152602.62999999998</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" ht="16">
-      <c r="A153" s="34" t="s">
+      <c r="C152" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E152" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F152" s="25" t="s">
         <v>264</v>
+      </c>
+      <c r="G152" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="H152" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I152" s="28">
+        <v>1139.84</v>
+      </c>
+      <c r="J152" s="28">
+        <v>140259.72</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" ht="16">
+      <c r="B153" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E153" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="F153" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G153" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="H153" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I153" s="28">
+        <v>3684.33</v>
+      </c>
+      <c r="J153" s="28">
+        <v>143944.05</v>
       </c>
     </row>
     <row r="154" spans="2:10" ht="16">
       <c r="B154" s="25" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
       <c r="C154" s="25" t="s">
         <v>6</v>
@@ -5885,22 +5974,22 @@
         <v>7</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="F154" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G154" s="25" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="H154" s="25" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="I154" s="28">
-        <v>387.0</v>
+        <v>2520.0</v>
       </c>
       <c r="J154" s="28">
-        <v>387.0</v>
+        <v>146464.05</v>
       </c>
     </row>
     <row r="155" spans="2:10" ht="16">
@@ -5914,56 +6003,56 @@
         <v>7</v>
       </c>
       <c r="E155" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F155" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="F155" s="25" t="s">
-        <v>270</v>
-      </c>
       <c r="G155" s="25" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="H155" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I155" s="28">
-        <v>140.33</v>
+        <v>6138.58</v>
       </c>
       <c r="J155" s="28">
-        <v>527.33</v>
+        <v>152602.62999999998</v>
       </c>
     </row>
     <row r="156" spans="2:10" ht="16">
       <c r="B156" s="25" t="s">
-        <v>271</v>
+        <v>112</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="D156" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G156" s="25" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="H156" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I156" s="28">
-        <v>-140.33</v>
+        <v>4303.02</v>
       </c>
       <c r="J156" s="28">
-        <v>387.0</v>
+        <v>156905.64999999997</v>
       </c>
     </row>
     <row r="157" spans="2:10" ht="16">
       <c r="B157" s="25" t="s">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>6</v>
@@ -5972,27 +6061,27 @@
         <v>7</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G157" s="25" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="H157" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I157" s="28">
-        <v>398.0</v>
+        <v>2520.0</v>
       </c>
       <c r="J157" s="28">
-        <v>785.0</v>
+        <v>159425.64999999997</v>
       </c>
     </row>
     <row r="158" spans="2:10" ht="16">
       <c r="B158" s="25" t="s">
-        <v>46</v>
+        <v>271</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>6</v>
@@ -6001,85 +6090,41 @@
         <v>7</v>
       </c>
       <c r="E158" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F158" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="G158" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="H158" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I158" s="28">
+        <v>1544.38</v>
+      </c>
+      <c r="J158" s="28">
+        <v>160970.02999999997</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="16">
+      <c r="A159" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="I159" s="29">
+        <f>I114+I115+I116+I117+I118+I119+I120+I121+I122+I123+I124+I125+I126+I127+I128+I129+I130+I131+I132+I133+I134+I135+I136+I137+I138+I139+I140+I141+I142+I143+I144+I145+I146+I147+I148+I149+I150+I151+I152+I153+I154+I155+I156+I157+I158</f>
+        <v>160970.02999999997</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="16">
+      <c r="A160" s="34" t="s">
         <v>275</v>
-      </c>
-      <c r="F158" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="G158" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="H158" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I158" s="28">
-        <v>800.0</v>
-      </c>
-      <c r="J158" s="28">
-        <v>1585.0</v>
-      </c>
-    </row>
-    <row r="159" spans="2:10" ht="16">
-      <c r="B159" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="C159" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D159" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E159" s="25" t="s">
-        <v>277</v>
-      </c>
-      <c r="F159" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="G159" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="H159" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I159" s="28">
-        <v>201.91</v>
-      </c>
-      <c r="J159" s="28">
-        <v>1786.91</v>
-      </c>
-    </row>
-    <row r="160" spans="2:10" ht="16">
-      <c r="B160" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C160" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D160" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E160" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="F160" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="G160" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="H160" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I160" s="28">
-        <v>917.0</v>
-      </c>
-      <c r="J160" s="28">
-        <v>2703.91</v>
       </c>
     </row>
     <row r="161" spans="2:10" ht="16">
       <c r="B161" s="25" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>6</v>
@@ -6088,114 +6133,114 @@
         <v>7</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G161" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="I161" s="28">
-        <v>503.18</v>
+        <v>387.0</v>
       </c>
       <c r="J161" s="28">
-        <v>3207.0899999999997</v>
+        <v>387.0</v>
       </c>
     </row>
     <row r="162" spans="2:10" ht="16">
       <c r="B162" s="25" t="s">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c r="C162" s="25" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="D162" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F162" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G162" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H162" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I162" s="28">
-        <v>-503.18</v>
+        <v>140.33</v>
       </c>
       <c r="J162" s="28">
-        <v>2703.91</v>
+        <v>527.33</v>
       </c>
     </row>
     <row r="163" spans="2:10" ht="16">
       <c r="B163" s="25" t="s">
-        <v>58</v>
+        <v>282</v>
       </c>
       <c r="C163" s="25" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="D163" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E163" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="F163" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="F163" s="25" t="s">
-        <v>284</v>
-      </c>
       <c r="G163" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H163" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I163" s="28">
-        <v>490.9</v>
+        <v>-140.33</v>
       </c>
       <c r="J163" s="28">
-        <v>3194.81</v>
+        <v>387.0</v>
       </c>
     </row>
     <row r="164" spans="2:10" ht="16">
       <c r="B164" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C164" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E164" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="F164" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="C164" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D164" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E164" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="F164" s="25" t="s">
-        <v>287</v>
-      </c>
       <c r="G164" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H164" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I164" s="28">
-        <v>179.74</v>
+        <v>398.0</v>
       </c>
       <c r="J164" s="28">
-        <v>3374.55</v>
+        <v>785.0</v>
       </c>
     </row>
     <row r="165" spans="2:10" ht="16">
       <c r="B165" s="25" t="s">
-        <v>288</v>
+        <v>46</v>
       </c>
       <c r="C165" s="25" t="s">
         <v>6</v>
@@ -6204,27 +6249,27 @@
         <v>7</v>
       </c>
       <c r="E165" s="25" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F165" s="25" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H165" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I165" s="28">
-        <v>674.26</v>
+        <v>800.0</v>
       </c>
       <c r="J165" s="28">
-        <v>4048.8100000000004</v>
+        <v>1585.0</v>
       </c>
     </row>
     <row r="166" spans="2:10" ht="16">
       <c r="B166" s="25" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>6</v>
@@ -6233,27 +6278,27 @@
         <v>7</v>
       </c>
       <c r="E166" s="25" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F166" s="25" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G166" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H166" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I166" s="28">
-        <v>400.0</v>
+        <v>201.91</v>
       </c>
       <c r="J166" s="28">
-        <v>4448.81</v>
+        <v>1786.91</v>
       </c>
     </row>
     <row r="167" spans="2:10" ht="16">
       <c r="B167" s="25" t="s">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="C167" s="25" t="s">
         <v>6</v>
@@ -6262,27 +6307,27 @@
         <v>7</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="F167" s="25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G167" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H167" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I167" s="28">
-        <v>400.0</v>
+        <v>917.0</v>
       </c>
       <c r="J167" s="28">
-        <v>4848.81</v>
+        <v>2703.91</v>
       </c>
     </row>
     <row r="168" spans="2:10" ht="16">
       <c r="B168" s="25" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="C168" s="25" t="s">
         <v>6</v>
@@ -6291,70 +6336,114 @@
         <v>7</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F168" s="25" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G168" s="25" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="H168" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I168" s="28">
-        <v>514.56</v>
+        <v>503.18</v>
       </c>
       <c r="J168" s="28">
-        <v>5363.370000000001</v>
+        <v>3207.0899999999997</v>
       </c>
     </row>
     <row r="169" spans="2:10" ht="16">
       <c r="B169" s="25" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="C169" s="25" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="D169" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E169" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="F169" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="G169" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="H169" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I169" s="28">
+        <v>-503.18</v>
+      </c>
+      <c r="J169" s="28">
+        <v>2703.91</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="16">
+      <c r="B170" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C170" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="F169" s="25" t="s">
+      <c r="F170" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="G169" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="H169" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I169" s="28">
-        <v>495.0</v>
-      </c>
-      <c r="J169" s="28">
-        <v>5858.370000000001</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ht="16">
-      <c r="A170" s="35" t="s">
+      <c r="G170" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="H170" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I170" s="28">
+        <v>490.9</v>
+      </c>
+      <c r="J170" s="28">
+        <v>3194.81</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="16">
+      <c r="B171" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="I170" s="29">
-        <f>I153+I154+I155+I156+I157+I158+I159+I160+I161+I162+I163+I164+I165+I166+I167+I168+I169</f>
-        <v>5858.370000000001</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" ht="16">
-      <c r="A171" s="34" t="s">
+      <c r="C171" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E171" s="25" t="s">
         <v>297</v>
+      </c>
+      <c r="F171" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="G171" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="H171" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I171" s="28">
+        <v>179.74</v>
+      </c>
+      <c r="J171" s="28">
+        <v>3374.55</v>
       </c>
     </row>
     <row r="172" spans="2:10" ht="16">
       <c r="B172" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C172" s="25" t="s">
         <v>6</v>
@@ -6363,56 +6452,56 @@
         <v>7</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G172" s="25" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="H172" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I172" s="28">
-        <v>7585.26</v>
+        <v>674.26</v>
       </c>
       <c r="J172" s="28">
-        <v>7585.26</v>
+        <v>4048.8100000000004</v>
       </c>
     </row>
     <row r="173" spans="2:10" ht="16">
       <c r="B173" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C173" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F173" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="C173" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D173" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E173" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="F173" s="25" t="s">
-        <v>304</v>
-      </c>
       <c r="G173" s="25" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="H173" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I173" s="28">
-        <v>17985.0</v>
+        <v>400.0</v>
       </c>
       <c r="J173" s="28">
-        <v>25570.260000000002</v>
+        <v>4448.81</v>
       </c>
     </row>
     <row r="174" spans="2:10" ht="16">
       <c r="B174" s="25" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="C174" s="25" t="s">
         <v>6</v>
@@ -6421,27 +6510,27 @@
         <v>7</v>
       </c>
       <c r="E174" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F174" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="F174" s="25" t="s">
-        <v>307</v>
-      </c>
       <c r="G174" s="25" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="H174" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I174" s="28">
-        <v>28775.8</v>
+        <v>400.0</v>
       </c>
       <c r="J174" s="28">
-        <v>54346.06</v>
+        <v>4848.81</v>
       </c>
     </row>
     <row r="175" spans="2:10" ht="16">
       <c r="B175" s="25" t="s">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="C175" s="25" t="s">
         <v>6</v>
@@ -6450,114 +6539,70 @@
         <v>7</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="F175" s="25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G175" s="25" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="H175" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I175" s="28">
-        <v>2125.17</v>
+        <v>514.56</v>
       </c>
       <c r="J175" s="28">
-        <v>56471.229999999996</v>
+        <v>5363.370000000001</v>
       </c>
     </row>
     <row r="176" spans="2:10" ht="16">
       <c r="B176" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="F176" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="G176" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="H176" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I176" s="28">
+        <v>495.0</v>
+      </c>
+      <c r="J176" s="28">
+        <v>5858.370000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="16">
+      <c r="A177" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="I177" s="29">
+        <f>I160+I161+I162+I163+I164+I165+I166+I167+I168+I169+I170+I171+I172+I173+I174+I175+I176</f>
+        <v>5858.370000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="16">
+      <c r="A178" s="34" t="s">
         <v>308</v>
-      </c>
-      <c r="C176" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="D176" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="E176" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="F176" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="G176" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="H176" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I176" s="28">
-        <v>-6787.25</v>
-      </c>
-      <c r="J176" s="28">
-        <v>49683.979999999996</v>
-      </c>
-    </row>
-    <row r="177" spans="2:10" ht="16">
-      <c r="B177" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C177" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D177" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E177" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="F177" s="25" t="s">
-        <v>313</v>
-      </c>
-      <c r="G177" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="H177" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I177" s="28">
-        <v>1982.88</v>
-      </c>
-      <c r="J177" s="28">
-        <v>51666.85999999999</v>
-      </c>
-    </row>
-    <row r="178" spans="2:10" ht="16">
-      <c r="B178" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C178" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D178" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E178" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="F178" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="G178" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="H178" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I178" s="28">
-        <v>1510.38</v>
-      </c>
-      <c r="J178" s="28">
-        <v>53177.23999999999</v>
       </c>
     </row>
     <row r="179" spans="2:10" ht="16">
       <c r="B179" s="25" t="s">
-        <v>149</v>
+        <v>309</v>
       </c>
       <c r="C179" s="25" t="s">
         <v>6</v>
@@ -6566,27 +6611,27 @@
         <v>7</v>
       </c>
       <c r="E179" s="25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F179" s="25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G179" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H179" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I179" s="28">
-        <v>1005.75</v>
+        <v>7585.26</v>
       </c>
       <c r="J179" s="28">
-        <v>54182.98999999999</v>
+        <v>7585.26</v>
       </c>
     </row>
     <row r="180" spans="2:10" ht="16">
       <c r="B180" s="25" t="s">
-        <v>44</v>
+        <v>313</v>
       </c>
       <c r="C180" s="25" t="s">
         <v>6</v>
@@ -6595,27 +6640,27 @@
         <v>7</v>
       </c>
       <c r="E180" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F180" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="G180" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H180" s="25" t="s">
         <v>316</v>
       </c>
-      <c r="G180" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="H180" s="25" t="s">
-        <v>11</v>
-      </c>
       <c r="I180" s="28">
-        <v>4740.45</v>
+        <v>17985.0</v>
       </c>
       <c r="J180" s="28">
-        <v>58923.43999999999</v>
+        <v>25570.260000000002</v>
       </c>
     </row>
     <row r="181" spans="2:10" ht="16">
       <c r="B181" s="25" t="s">
-        <v>44</v>
+        <v>317</v>
       </c>
       <c r="C181" s="25" t="s">
         <v>6</v>
@@ -6624,27 +6669,27 @@
         <v>7</v>
       </c>
       <c r="E181" s="25" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="F181" s="25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G181" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H181" s="25" t="s">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="I181" s="28">
-        <v>8141.36</v>
+        <v>28775.8</v>
       </c>
       <c r="J181" s="28">
-        <v>67064.79999999999</v>
+        <v>54346.06</v>
       </c>
     </row>
     <row r="182" spans="2:10" ht="16">
       <c r="B182" s="25" t="s">
-        <v>46</v>
+        <v>319</v>
       </c>
       <c r="C182" s="25" t="s">
         <v>6</v>
@@ -6653,56 +6698,56 @@
         <v>7</v>
       </c>
       <c r="E182" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F182" s="25" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G182" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H182" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I182" s="28">
-        <v>1326.38</v>
+        <v>2125.17</v>
       </c>
       <c r="J182" s="28">
-        <v>68391.18</v>
+        <v>56471.229999999996</v>
       </c>
     </row>
     <row r="183" spans="2:10" ht="16">
       <c r="B183" s="25" t="s">
-        <v>50</v>
+        <v>319</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>7</v>
+        <v>199</v>
       </c>
       <c r="E183" s="25" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="F183" s="25" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G183" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H183" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I183" s="28">
-        <v>42912.69</v>
+        <v>-6787.25</v>
       </c>
       <c r="J183" s="28">
-        <v>111303.87</v>
+        <v>49683.979999999996</v>
       </c>
     </row>
     <row r="184" spans="2:10" ht="16">
       <c r="B184" s="25" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C184" s="25" t="s">
         <v>6</v>
@@ -6711,27 +6756,27 @@
         <v>7</v>
       </c>
       <c r="E184" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F184" s="25" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G184" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H184" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I184" s="28">
-        <v>1259.23</v>
+        <v>1982.88</v>
       </c>
       <c r="J184" s="28">
-        <v>112563.09999999999</v>
+        <v>51666.85999999999</v>
       </c>
     </row>
     <row r="185" spans="2:10" ht="16">
       <c r="B185" s="25" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C185" s="25" t="s">
         <v>6</v>
@@ -6740,27 +6785,27 @@
         <v>7</v>
       </c>
       <c r="E185" s="25" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="F185" s="25" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G185" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H185" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I185" s="28">
-        <v>1544.93</v>
+        <v>1510.38</v>
       </c>
       <c r="J185" s="28">
-        <v>114108.02999999998</v>
+        <v>53177.23999999999</v>
       </c>
     </row>
     <row r="186" spans="2:10" ht="16">
       <c r="B186" s="25" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C186" s="25" t="s">
         <v>6</v>
@@ -6769,27 +6814,27 @@
         <v>7</v>
       </c>
       <c r="E186" s="25" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F186" s="25" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G186" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H186" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I186" s="28">
-        <v>9386.35</v>
+        <v>1005.75</v>
       </c>
       <c r="J186" s="28">
-        <v>123494.37999999999</v>
+        <v>54182.98999999999</v>
       </c>
     </row>
     <row r="187" spans="2:10" ht="16">
       <c r="B187" s="25" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="C187" s="25" t="s">
         <v>6</v>
@@ -6798,27 +6843,27 @@
         <v>7</v>
       </c>
       <c r="E187" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F187" s="25" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G187" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H187" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I187" s="28">
-        <v>2225.32</v>
+        <v>4740.45</v>
       </c>
       <c r="J187" s="28">
-        <v>125719.7</v>
+        <v>58923.43999999999</v>
       </c>
     </row>
     <row r="188" spans="2:10" ht="16">
       <c r="B188" s="25" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="C188" s="25" t="s">
         <v>6</v>
@@ -6827,27 +6872,27 @@
         <v>7</v>
       </c>
       <c r="E188" s="25" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="F188" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G188" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H188" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I188" s="28">
-        <v>7200.0</v>
+        <v>8141.36</v>
       </c>
       <c r="J188" s="28">
-        <v>132919.7</v>
+        <v>67064.79999999999</v>
       </c>
     </row>
     <row r="189" spans="2:10" ht="16">
       <c r="B189" s="25" t="s">
-        <v>326</v>
+        <v>46</v>
       </c>
       <c r="C189" s="25" t="s">
         <v>6</v>
@@ -6856,27 +6901,27 @@
         <v>7</v>
       </c>
       <c r="E189" s="25" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="F189" s="25" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G189" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H189" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I189" s="28">
-        <v>27724.37</v>
+        <v>1326.38</v>
       </c>
       <c r="J189" s="28">
-        <v>160644.07</v>
+        <v>68391.18</v>
       </c>
     </row>
     <row r="190" spans="2:10" ht="16">
       <c r="B190" s="25" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C190" s="25" t="s">
         <v>6</v>
@@ -6885,27 +6930,27 @@
         <v>7</v>
       </c>
       <c r="E190" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F190" s="25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G190" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H190" s="25" t="s">
-        <v>11</v>
+        <v>316</v>
       </c>
       <c r="I190" s="28">
-        <v>16947.18</v>
+        <v>42912.69</v>
       </c>
       <c r="J190" s="28">
-        <v>177591.25</v>
+        <v>111303.87</v>
       </c>
     </row>
     <row r="191" spans="2:10" ht="16">
       <c r="B191" s="25" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="C191" s="25" t="s">
         <v>6</v>
@@ -6914,27 +6959,27 @@
         <v>7</v>
       </c>
       <c r="E191" s="25" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F191" s="25" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G191" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H191" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I191" s="28">
-        <v>7957.68</v>
+        <v>1259.23</v>
       </c>
       <c r="J191" s="28">
-        <v>185548.93</v>
+        <v>112563.09999999999</v>
       </c>
     </row>
     <row r="192" spans="2:10" ht="16">
       <c r="B192" s="25" t="s">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="C192" s="25" t="s">
         <v>6</v>
@@ -6943,27 +6988,27 @@
         <v>7</v>
       </c>
       <c r="E192" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F192" s="25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G192" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H192" s="25" t="s">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="I192" s="28">
-        <v>4709.5</v>
+        <v>1544.93</v>
       </c>
       <c r="J192" s="28">
-        <v>190258.43</v>
+        <v>114108.02999999998</v>
       </c>
     </row>
     <row r="193" spans="2:10" ht="16">
       <c r="B193" s="25" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C193" s="25" t="s">
         <v>6</v>
@@ -6972,27 +7017,27 @@
         <v>7</v>
       </c>
       <c r="E193" s="25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F193" s="25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G193" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H193" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I193" s="28">
-        <v>4456.51</v>
+        <v>9386.35</v>
       </c>
       <c r="J193" s="28">
-        <v>194714.94</v>
+        <v>123494.37999999999</v>
       </c>
     </row>
     <row r="194" spans="2:10" ht="16">
       <c r="B194" s="25" t="s">
-        <v>333</v>
+        <v>232</v>
       </c>
       <c r="C194" s="25" t="s">
         <v>6</v>
@@ -7001,27 +7046,27 @@
         <v>7</v>
       </c>
       <c r="E194" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F194" s="25" t="s">
         <v>334</v>
       </c>
       <c r="G194" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H194" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I194" s="28">
-        <v>5705.71</v>
+        <v>2225.32</v>
       </c>
       <c r="J194" s="28">
-        <v>200420.65</v>
+        <v>125719.7</v>
       </c>
     </row>
     <row r="195" spans="2:10" ht="16">
       <c r="B195" s="25" t="s">
-        <v>240</v>
+        <v>335</v>
       </c>
       <c r="C195" s="25" t="s">
         <v>6</v>
@@ -7030,27 +7075,27 @@
         <v>7</v>
       </c>
       <c r="E195" s="25" t="s">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="F195" s="25" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G195" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H195" s="25" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="I195" s="28">
-        <v>44271.2</v>
+        <v>7200.0</v>
       </c>
       <c r="J195" s="28">
-        <v>244691.84999999998</v>
+        <v>132919.7</v>
       </c>
     </row>
     <row r="196" spans="2:10" ht="16">
       <c r="B196" s="25" t="s">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="C196" s="25" t="s">
         <v>6</v>
@@ -7059,27 +7104,27 @@
         <v>7</v>
       </c>
       <c r="E196" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F196" s="25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G196" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H196" s="25" t="s">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="I196" s="28">
-        <v>2575.25</v>
+        <v>27724.37</v>
       </c>
       <c r="J196" s="28">
-        <v>247267.09999999998</v>
+        <v>160644.07</v>
       </c>
     </row>
     <row r="197" spans="2:10" ht="16">
       <c r="B197" s="25" t="s">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="C197" s="25" t="s">
         <v>6</v>
@@ -7088,27 +7133,27 @@
         <v>7</v>
       </c>
       <c r="E197" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F197" s="25" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G197" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H197" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I197" s="28">
-        <v>5046.2</v>
+        <v>16947.18</v>
       </c>
       <c r="J197" s="28">
-        <v>252313.3</v>
+        <v>177591.25</v>
       </c>
     </row>
     <row r="198" spans="2:10" ht="16">
       <c r="B198" s="25" t="s">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="C198" s="25" t="s">
         <v>6</v>
@@ -7117,27 +7162,27 @@
         <v>7</v>
       </c>
       <c r="E198" s="25" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F198" s="25" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G198" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H198" s="25" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="I198" s="28">
-        <v>5224.91</v>
+        <v>7957.68</v>
       </c>
       <c r="J198" s="28">
-        <v>257538.21</v>
+        <v>185548.93</v>
       </c>
     </row>
     <row r="199" spans="2:10" ht="16">
       <c r="B199" s="25" t="s">
-        <v>137</v>
+        <v>341</v>
       </c>
       <c r="C199" s="25" t="s">
         <v>6</v>
@@ -7146,27 +7191,27 @@
         <v>7</v>
       </c>
       <c r="E199" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F199" s="25" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G199" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H199" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I199" s="28">
-        <v>916.98</v>
+        <v>4709.5</v>
       </c>
       <c r="J199" s="28">
-        <v>258455.19</v>
+        <v>190258.43</v>
       </c>
     </row>
     <row r="200" spans="2:10" ht="16">
       <c r="B200" s="25" t="s">
-        <v>341</v>
+        <v>139</v>
       </c>
       <c r="C200" s="25" t="s">
         <v>6</v>
@@ -7175,27 +7220,27 @@
         <v>7</v>
       </c>
       <c r="E200" s="25" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F200" s="25" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G200" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H200" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I200" s="28">
-        <v>11243.19</v>
+        <v>4456.51</v>
       </c>
       <c r="J200" s="28">
-        <v>269698.38</v>
+        <v>194714.94</v>
       </c>
     </row>
     <row r="201" spans="2:10" ht="16">
       <c r="B201" s="25" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="C201" s="25" t="s">
         <v>6</v>
@@ -7204,27 +7249,27 @@
         <v>7</v>
       </c>
       <c r="E201" s="25" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F201" s="25" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G201" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H201" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I201" s="28">
-        <v>5565.89</v>
+        <v>5705.71</v>
       </c>
       <c r="J201" s="28">
-        <v>275264.27</v>
+        <v>200420.65</v>
       </c>
     </row>
     <row r="202" spans="2:10" ht="16">
       <c r="B202" s="25" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C202" s="25" t="s">
         <v>6</v>
@@ -7233,41 +7278,85 @@
         <v>7</v>
       </c>
       <c r="E202" s="25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F202" s="25" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G202" s="25" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H202" s="25" t="s">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="I202" s="28">
-        <v>5025.97</v>
+        <v>44271.2</v>
       </c>
       <c r="J202" s="28">
-        <v>280290.24</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" ht="16">
-      <c r="A203" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="I203" s="29">
-        <f>I171+I172+I173+I174+I175+I176+I177+I178+I179+I180+I181+I182+I183+I184+I185+I186+I187+I188+I189+I190+I191+I192+I193+I194+I195+I196+I197+I198+I199+I200+I201+I202</f>
-        <v>280290.24</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" ht="16">
-      <c r="A204" s="34" t="s">
-        <v>346</v>
+        <v>244691.84999999998</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" ht="16">
+      <c r="B203" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C203" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E203" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F203" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="G203" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H203" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I203" s="28">
+        <v>2575.25</v>
+      </c>
+      <c r="J203" s="28">
+        <v>247267.09999999998</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" ht="16">
+      <c r="B204" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="C204" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E204" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F204" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="G204" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H204" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I204" s="28">
+        <v>5046.2</v>
+      </c>
+      <c r="J204" s="28">
+        <v>252313.3</v>
       </c>
     </row>
     <row r="205" spans="2:10" ht="16">
       <c r="B205" s="25" t="s">
-        <v>347</v>
+        <v>184</v>
       </c>
       <c r="C205" s="25" t="s">
         <v>6</v>
@@ -7276,85 +7365,85 @@
         <v>7</v>
       </c>
       <c r="E205" s="25" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="F205" s="25" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G205" s="25" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="H205" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I205" s="28">
-        <v>1772.85</v>
+        <v>5224.91</v>
       </c>
       <c r="J205" s="28">
-        <v>1772.85</v>
+        <v>257538.21</v>
       </c>
     </row>
     <row r="206" spans="2:10" ht="16">
       <c r="B206" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C206" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E206" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F206" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="C206" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D206" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E206" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F206" s="25" t="s">
-        <v>352</v>
-      </c>
       <c r="G206" s="25" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="H206" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I206" s="28">
-        <v>774.93</v>
+        <v>916.98</v>
       </c>
       <c r="J206" s="28">
-        <v>2547.7799999999997</v>
+        <v>258455.19</v>
       </c>
     </row>
     <row r="207" spans="2:10" ht="16">
       <c r="B207" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="C207" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E207" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F207" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="C207" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D207" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E207" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F207" s="25" t="s">
-        <v>354</v>
-      </c>
       <c r="G207" s="25" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="H207" s="25" t="s">
         <v>11</v>
       </c>
       <c r="I207" s="28">
-        <v>1361.73</v>
+        <v>11243.19</v>
       </c>
       <c r="J207" s="28">
-        <v>3909.5099999999998</v>
+        <v>269698.38</v>
       </c>
     </row>
     <row r="208" spans="2:10" ht="16">
       <c r="B208" s="25" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="C208" s="25" t="s">
         <v>6</v>
@@ -7363,27 +7452,27 @@
         <v>7</v>
       </c>
       <c r="E208" s="25" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="F208" s="25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G208" s="25" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="H208" s="25" t="s">
-        <v>357</v>
+        <v>11</v>
       </c>
       <c r="I208" s="28">
-        <v>1354.59</v>
+        <v>5565.89</v>
       </c>
       <c r="J208" s="28">
-        <v>5264.099999999999</v>
+        <v>275264.27</v>
       </c>
     </row>
     <row r="209" spans="2:10" ht="16">
       <c r="B209" s="25" t="s">
-        <v>358</v>
+        <v>266</v>
       </c>
       <c r="C209" s="25" t="s">
         <v>6</v>
@@ -7392,83 +7481,387 @@
         <v>7</v>
       </c>
       <c r="E209" s="25" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="F209" s="25" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G209" s="25" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="H209" s="25" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="I209" s="28">
-        <v>1188.16</v>
+        <v>5025.97</v>
       </c>
       <c r="J209" s="28">
-        <v>6452.259999999999</v>
+        <v>280290.24</v>
       </c>
     </row>
     <row r="210" spans="2:10" ht="16">
       <c r="B210" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C210" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E210" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F210" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="G210" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H210" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I210" s="28">
+        <v>3853.71</v>
+      </c>
+      <c r="J210" s="28">
+        <v>284143.95</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" ht="16">
+      <c r="B211" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C211" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E211" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="F211" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="G211" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H211" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="I211" s="28">
+        <v>71562.65</v>
+      </c>
+      <c r="J211" s="28">
+        <v>355706.6</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" ht="16">
+      <c r="B212" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C212" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E212" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F212" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="G212" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H212" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I212" s="28">
+        <v>7669.86</v>
+      </c>
+      <c r="J212" s="28">
+        <v>363376.45999999996</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" ht="16">
+      <c r="B213" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C213" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D213" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E213" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F213" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="G213" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H213" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I213" s="28">
+        <v>521.25</v>
+      </c>
+      <c r="J213" s="28">
+        <v>363897.70999999996</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="16">
+      <c r="B214" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C214" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D214" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E214" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F214" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="G214" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="H214" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I214" s="28">
+        <v>68.66</v>
+      </c>
+      <c r="J214" s="28">
+        <v>363966.36999999994</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="16">
+      <c r="A215" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="I215" s="29">
+        <f>I178+I179+I180+I181+I182+I183+I184+I185+I186+I187+I188+I189+I190+I191+I192+I193+I194+I195+I196+I197+I198+I199+I200+I201+I202+I203+I204+I205+I206+I207+I208+I209+I210+I211+I212+I213+I214</f>
+        <v>363966.36999999994</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" ht="16">
+      <c r="A216" s="34" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="16">
+      <c r="B217" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="C217" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E217" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F217" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="G217" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H217" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I217" s="28">
+        <v>1772.85</v>
+      </c>
+      <c r="J217" s="28">
+        <v>1772.85</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" ht="16">
+      <c r="B218" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C218" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E218" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F218" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="G218" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H218" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I218" s="28">
+        <v>774.93</v>
+      </c>
+      <c r="J218" s="28">
+        <v>2547.7799999999997</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" ht="16">
+      <c r="B219" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="C219" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E219" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F219" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="G219" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H219" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I219" s="28">
+        <v>1361.73</v>
+      </c>
+      <c r="J219" s="28">
+        <v>3909.5099999999998</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" ht="16">
+      <c r="B220" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="C220" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E220" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="F220" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="G220" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H220" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="I220" s="28">
+        <v>1354.59</v>
+      </c>
+      <c r="J220" s="28">
+        <v>5264.099999999999</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" ht="16">
+      <c r="B221" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="C221" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D221" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E221" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F221" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="G221" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H221" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I221" s="28">
+        <v>1188.16</v>
+      </c>
+      <c r="J221" s="28">
+        <v>6452.259999999999</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" ht="16">
+      <c r="B222" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C210" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D210" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E210" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F210" s="25" t="s">
-        <v>360</v>
-      </c>
-      <c r="G210" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="H210" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="I210" s="28">
+      <c r="C222" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E222" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F222" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="G222" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H222" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I222" s="28">
         <v>1471.3</v>
       </c>
-      <c r="J210" s="28">
+      <c r="J222" s="28">
         <v>7923.5599999999995</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="16">
-      <c r="A211" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="I211" s="29">
-        <f>I204+I205+I206+I207+I208+I209+I210</f>
+    <row r="223" spans="1:9" ht="16">
+      <c r="A223" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="I223" s="29">
+        <f>I216+I217+I218+I219+I220+I221+I222</f>
         <v>7923.5599999999995</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="16">
-      <c r="A212" s="36" t="s">
-        <v>362</v>
-      </c>
-      <c r="I212" s="29">
-        <f>I58+I78+I102+I109+I152+I170+I203+I211</f>
-        <v>1078492.7200000002</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" ht="16">
-      <c r="A213" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="I213" s="29">
-        <f>I212</f>
-        <v>1078492.7200000002</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" ht="16">
-      <c r="A217" s="38" t="s">
-        <v>373</v>
+    <row r="224" spans="1:9" ht="16">
+      <c r="A224" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="I224" s="29">
+        <f>I60+I81+I106+I113+I159+I177+I215+I223</f>
+        <v>1228782.09</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="16">
+      <c r="A225" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="I225" s="29">
+        <f>I224</f>
+        <v>1228782.09</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="16">
+      <c r="A229" s="38" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -7476,7 +7869,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A217:I217"/>
+    <mergeCell ref="A229:I229"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
